--- a/01_pedidos.xlsx
+++ b/01_pedidos.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="1" r:id="R9471ee47b8684e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kits_SMED" sheetId="2" r:id="R4e7ba8636fc24ea2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="3" r:id="R6cce162081ef47f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="1" r:id="Rc730f7742e9641e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kits_SMED" sheetId="2" r:id="R42cfef848ee84a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="3" r:id="R424f72e238d84645"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -61,7 +61,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -116,6 +116,7 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -611,7 +612,7 @@
         <x:v>46267</x:v>
       </x:c>
       <x:c r="D8" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E8" s="21" t="str">
         <x:v>Media</x:v>
@@ -716,7 +717,7 @@
         <x:v>46293</x:v>
       </x:c>
       <x:c r="D11" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="E11" s="21" t="str">
         <x:v>Baja</x:v>
@@ -751,7 +752,7 @@
         <x:v>46288</x:v>
       </x:c>
       <x:c r="D12" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="E12" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1066,7 +1067,7 @@
         <x:v>46277</x:v>
       </x:c>
       <x:c r="D21" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E21" s="21" t="str">
         <x:v>Alta</x:v>
@@ -1416,7 +1417,7 @@
         <x:v>46279</x:v>
       </x:c>
       <x:c r="D31" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E31" s="21" t="str">
         <x:v>Media</x:v>
@@ -1451,7 +1452,7 @@
         <x:v>46278</x:v>
       </x:c>
       <x:c r="D32" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E32" s="21" t="str">
         <x:v>Media</x:v>
@@ -1486,7 +1487,7 @@
         <x:v>46272</x:v>
       </x:c>
       <x:c r="D33" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E33" s="21" t="str">
         <x:v>Media</x:v>
@@ -2151,7 +2152,7 @@
         <x:v>46304</x:v>
       </x:c>
       <x:c r="D52" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="E52" s="21" t="str">
         <x:v>Media</x:v>
@@ -2256,7 +2257,7 @@
         <x:v>46300</x:v>
       </x:c>
       <x:c r="D55" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="E55" s="21" t="str">
         <x:v>Alta</x:v>
@@ -2431,7 +2432,7 @@
         <x:v>46309</x:v>
       </x:c>
       <x:c r="D60" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E60" s="21" t="str">
         <x:v>Media</x:v>
@@ -2672,7 +2673,7 @@
         <x:v>46310</x:v>
       </x:c>
       <x:c r="D67" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="E67" s="21" t="str">
         <x:v>Baja</x:v>
@@ -2837,7 +2838,7 @@
         <x:v>46313</x:v>
       </x:c>
       <x:c r="D72" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="E72" s="21" t="str">
         <x:v>Media</x:v>
@@ -2903,7 +2904,7 @@
         <x:v>46313</x:v>
       </x:c>
       <x:c r="D74" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="E74" s="21" t="str">
         <x:v>Media</x:v>
@@ -3011,9 +3012,14 @@
       <x:formula>I5="Bloqueado"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D76">
+      <x:formula1>"Gala,Novia,Quinceañera"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cd3902f66de4f84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28b9aece5ff141ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6125,7 +6131,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd11348a31dd949c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb68cb38cc08c40ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6186,6 +6192,14 @@
         <x:v>Tiempo consumido en la preparación del kit antes de producción.</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="21" t="str">
+        <x:v>Tipo_Vestido</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="str">
+        <x:v>Solo se permiten: Gala, Novia y Quinceañera.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
